--- a/odoo_nhs_dspt/static/import_templates/dspt_evidence_answers_import_template.xlsx
+++ b/odoo_nhs_dspt/static/import_templates/dspt_evidence_answers_import_template.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,57 +414,327 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>assessment_id/edition_id/year</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>evidence_def_id/reference</t>
+          <t>assessment_id/id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>assertion_id/id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>evidence_def_id/id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>evidence_ref</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>evidence_review_date</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>owner_id/login</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>owner_id/id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>odoo_nhs_dspt.demo_evidence_line_1_1_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>odoo_nhs_dspt.demo_assessment_2025_26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>odoo_nhs_dspt.demo_assertion_line_1_1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>odoo_nhs_dspt.evidence_1_1_1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sample answer — carried forward from last year's paper submission.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Policy ref DPO-2024-01</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>base.user_admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>odoo_nhs_dspt.demo_evidence_line_2_1_1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>odoo_nhs_dspt.demo_assessment_2025_26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>odoo_nhs_dspt.demo_assertion_line_2_1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>odoo_nhs_dspt.evidence_2_1_1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sample answer — carried forward from last year's paper submission.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HR training log 2024</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>base.user_admin</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>HOW THE 'id' COLUMNS WORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Odoo's generic import can only match an EXISTING related record via its External ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(the 'xxx_id/id' columns below) or its database id — it cannot create a missing parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>record on the fly from a name/code/reference value. The sample rows below reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>the External IDs shipped with this module's seed data, so they import cleanly as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>'id' (first column): assigns a NEW External ID to the row you are creating. Do NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>prefix it with 'odoo_nhs_dspt.' (or any other installed module's name) — Odoo will</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>refuse the import, because a record filed under another module's prefix gets deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>the next time that module is upgraded. Use the '__import__.' prefix instead (Odoo's</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>own recommended convention for imported data), e.g. '__import__.my_new_standard_2027'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>To find the External ID of a record you created yourself (for the 'xxx_id/id' lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>columns): enable Developer Mode (Settings &gt; General Settings &gt; Developer Tools), open</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>the record, then Actions (gear icon) &gt; View Metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>THIS SHEET: fills in answers for 2 evidence items on the demo assessment shipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>with this module (only present if you installed with demo data). It creates the</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>evidence lines directly under an existing assertion line and assessment — normally</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>used to reconstruct a prior year's answers that were never tracked in this system</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>before, rather than as a substitute for the in-app 'Carry Forward' action on an</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>assessment that already has lines generated via the Generate button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>This sheet has no 'id' column of its own because the evidence line's identity here</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>comes from the assessment + evidence definition it belongs to, not a standalone key.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
